--- a/Mechanical_Department_Input.xlsx
+++ b/Mechanical_Department_Input.xlsx
@@ -10,7 +10,33 @@
     <sheet name="Pulleys" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Belts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Idlers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Drive Units" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Skirt Board Assembly" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Belt Cleaners" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Motors" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gearbox" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Coupling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Hyd. Thruster" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Take up components" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Technological Structures" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Chute Work" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Accessories" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Hoists &amp; Electric Winches" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Divertor gate" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Road gate" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Slide gate" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="CBMS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Metal Detector" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Coal Sampler" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Belt Weigher" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Hopper" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Secondary sizer" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Vibrating feeder" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Truck Loading system" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Rapid Wagon loading system" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Stacker cum Reclaimer" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="IPC (Skid Mounted System)" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Shifting of IPC system" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Workshop" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,33 +537,763 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>800 x 20 x Ceramic x 180</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1400 mm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x travel x winch</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gravity Take Up x 6m Travel x Pulley &amp; Frame Package</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conveyor Tensioning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Elecon Engineering</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D2" t="n">
+        <v>210000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Includes bend pulleys, counterweight frame and safety guides</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>stand/stringers x decking x frame x fasteners x seal plate</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Weight per Meter</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Stand &amp; Stringers x 3mm Decking Plate x Heavy Frame x High Tensile Fasteners x Rubber Seal Plate</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>120 kg/m</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tata Bluescope</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Complete structural package per meter including decking and fasteners</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sailhard liner x ms plate x contingency x bolt nut</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10mm SAILHARD Liner x 12mm MS Plate x Contingency Structural x Gr 8.8 Bolt Nut</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1 Ton Lot</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SAIL Fabrication</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>135000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>High abrasion resistant transfer chute fabricated package per MT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>wire mesh x conveyor hood</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Galvanized Wire Mesh Guard x Color Coated Conveyor Hood</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conveyor Safety &amp; Weather Protection</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Interarch Building</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rate per linear meter of conveyor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x lift x speed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5 Ton x 12m Lift x 6m/min Electric Chain Hoist</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Motorized Trolley Type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Indef (Bajaj)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>145000</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-02-20</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>High tension head pulley</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy duty maintenance hoist for transfer tower</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x actuation x liner</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Chute Size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2-Way Flapper x Pneumatic Cylinder x 10mm AR Plate</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Elecon Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>285000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Motorized/Pneumatic divertor gate for stream splitting</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x size x motor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Motorized Heavy Duty Road Gate x 1200x1200mm x 1.5kW Drive</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Emergency Cut-off</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Macmet India</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>210000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy duty motorized rack and pinion road gate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x size x operation</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rack &amp; Pinion Slide Gate x 800x800mm x Manual Wheel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hopper Outlet Maintenance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Macmet India</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Manual handwheel operated maintenance slide gate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>system x sensors x interface</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Conveyor Belt Monitoring System x 4 Optical Scanners x Ethernet/IP SCADA Interface</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Real-time Rip &amp; Wear Detection</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CBGuard Technologies</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Complete optical &amp; magnetic belt rip detection system</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x belt width x sensitivity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aperture Type x 1400mm Belt x 15mm Ferrous/Non-Ferrous Sensitivity</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tramp Iron Protection</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Eriez Magnetics</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>320000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>High sensitivity industrial metal detector with bag marker</t>
         </is>
       </c>
     </row>
@@ -552,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,33 +1403,763 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1400 x 5 x HR-Grade</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EP-1000</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bridgestone</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4800</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Heat resistant up to 180 deg C</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>system x cutter x sample size</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cross Belt Auto Sampler x Primary &amp; Secondary Cutter x 50kg/hr Sample</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASTM/ISO Compliant</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Two stage automatic mechanical sampling system</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>idlers x load cells x accuracy</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4-Idler Electronic Belt Scale x 4 Hermetic Load Cells x +/- 0.25% Accuracy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fiscal / Inventory Weighing</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Schenck Process</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>420000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>High precision belt scale with microprocessor integrator</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x structure x liner</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1 x 500 T x Heavy RCC &amp; Structural Steel Grid x 12mm SAILHARD Lined</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Crusher Feed Hopper</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L&amp;T Heavy Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>500 Ton capacity surge hopper complete with liners and grid</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x shaft x teeth</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1000/1100 TPH x Twin Shaft Toothed Sizer x Hardfaced Alloy Teeth</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Secondary Crushing</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MMD Sizers</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy duty mineral sizer complete with drives and fluid couplings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x drive x deck</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1000/1100 TPH x Dual Unbalanced Motor Drive x Abrasion Resistant Deck</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hopper Discharge Feeder</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Joest India</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy duty electromechanical vibrating feeder</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x hopper x chute</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2 x 150T x Batch Weigh Hopper System x Hydraulic Telescopic Chute</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automated Truck Dispatch</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FLSmidth</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>14500000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Complete dual batch weigh truck loading system</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>silo capacity x gate x hydraulic power</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4000 Ton RCC Silo x Flood Loading Gate x 45kW Hydraulic Power Pack</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train Rapid Loading (TLO)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Elecon Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>33550000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Automated train loading station complete mechanical package</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x boom x mounting</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4000/4400 TPH x 35m Boom Length x Rail Mounted Sleewing &amp; Luffing</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stockyard Yard Machine</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ThyssenKrupp India</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>329400000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bucket wheel stacker cum reclaimer complete machine</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>capacity x hoppers x feeder</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2000/2200 TPH x 4 x 250T Hopper x Apron Feeder &amp; Secondary Sizer Package</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>In-Pit Crushing &amp; Conveying</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Metso Outotec</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>287811000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Complete mobile/skid mounted crushing station</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>system x transport x hydraulics</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Heavy Lifting Skid &amp; Hydraulic Transport Package x 500 Ton Lift Capacity</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>In-Pit Station Relocation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mammoet India</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>87745655</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Specialized heavy transport and hydraulic crawling system</t>
         </is>
       </c>
     </row>
@@ -688,7 +2174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,91 +2239,289 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>114 x 380 x 20</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Return Roller</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>package x cranes x tools</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Conveyor Maintenance Workshop Equipment Package x 10T EOT Crane &amp; Lathe/Drill Machines</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Plant Central Maintenance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HMT Machine Tools</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Comprehensive mechanical workshop machinery and EOT crane</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dia x len x spec</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1200mm x 6m x Heavy Duty AR Lined</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conveyor Loading Zone</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Elecon Engineering</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1350</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Heavy wall steel tube</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Motor Power x Gearbox Ratio</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Mounting Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Vendor Name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Base Rate</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Quote Date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>75 kW x 25:1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Foot Mounted</t>
+      <c r="D2" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Includes rubber sealing strips and quick release clamps</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x blade x tensioner</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Belt Width</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Primary &amp; Secondary x Tungsten Carbide x Spring Loaded</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1200 mm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Martin Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy duty scraper set with tungsten carbide tips</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>power x rpm x eff</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mounting</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>75 kW x 1500 RPM x IE3 Premium Efficiency</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Foot Mounted B3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -846,7 +2530,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>340000</v>
+        <v>185000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -855,37 +2539,235 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IE3 premium efficiency motor with helical bevel gearbox</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>45 kW x 20:1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Flange Mounted</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>IE3 energy efficient induction motor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x ratio x shaft</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Helical Bevel x 25:1 x Solid Shaft Output</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>75 kW Drive</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>SEW Eurodrive</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D2" t="n">
         <v>265000</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2024-04-18</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Heavy duty outdoor conveyor drive unit</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy duty outdoor conveyor gear unit with cooling fan</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x rating x size</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fluid Coupling x 100 kW x Size 480</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Motor to Gearbox</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Voith Turbo</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Constant fill fluid coupling with delay chamber</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type x drum dia x thrust</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Vendor Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quote Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Electro Hydraulic Thruster Brake x 300mm x 50kg Thrust</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conveyor Holdback/Brake</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pethe Industrial</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>High reliability thruster brake unit</t>
         </is>
       </c>
     </row>
